--- a/competitions_list.xlsx
+++ b/competitions_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mussab/Desktop/Softec/Ambbasdor/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F75A8160-9D4F-8F44-9ED5-5C98EBA4B8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762C38ED-C492-554C-9D6F-434AFFA221D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21580" xr2:uid="{D5482571-2A51-A645-9BC1-90DDEFF32912}"/>
   </bookViews>
@@ -303,7 +303,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,###"/>
+  </numFmts>
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -452,6 +455,13 @@
     </font>
     <font>
       <sz val="26"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -835,16 +845,18 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1374,382 +1386,381 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92310E42-BC94-B24F-90E1-BF0CFF27487F}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
     <col min="2" max="2" width="36.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.5" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" customWidth="1"/>
+    <col min="4" max="4" width="26.1640625" customWidth="1"/>
     <col min="5" max="5" width="17.83203125" customWidth="1"/>
     <col min="6" max="6" width="31.6640625" customWidth="1"/>
     <col min="7" max="7" width="33.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="9"/>
-    </row>
-    <row r="2" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="7">
         <v>100000</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="7">
         <v>50000</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <v>5000</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <v>2</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="7">
         <v>60000</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="7">
         <v>30000</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="7">
         <v>2500</v>
       </c>
-      <c r="F3" s="7">
-        <v>1</v>
-      </c>
-      <c r="G3" s="7">
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="7">
         <v>30000</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="7">
         <v>15000</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <v>1700</v>
       </c>
-      <c r="F4" s="7">
-        <v>1</v>
-      </c>
-      <c r="G4" s="7">
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="7">
         <v>25000</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="7">
         <v>10000</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <v>1700</v>
       </c>
-      <c r="F5" s="7">
-        <v>1</v>
-      </c>
-      <c r="G5" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F5" s="6">
+        <v>1</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
         <v>20000</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="7">
         <v>10000</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <v>1500</v>
       </c>
-      <c r="F6" s="7">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F6" s="6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <v>50000</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <v>25000</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>2000</v>
       </c>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7">
+      <c r="F7" s="6">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <v>70000</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="7">
         <v>35000</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>3000</v>
       </c>
-      <c r="F8" s="7">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7">
+      <c r="F8" s="6">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <v>20000</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="7">
         <v>10000</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>1500</v>
       </c>
-      <c r="F9" s="7">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F9" s="6">
+        <v>1</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <v>50000</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="7">
         <v>25000</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>2500</v>
       </c>
-      <c r="F10" s="7">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7">
+      <c r="F10" s="6">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>20000</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="7">
         <v>10000</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>2000</v>
       </c>
-      <c r="F11" s="7">
-        <v>1</v>
-      </c>
-      <c r="G11" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F11" s="6">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <v>25000</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <v>20000</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>3000</v>
       </c>
-      <c r="F12" s="7">
-        <v>1</v>
-      </c>
-      <c r="G12" s="7">
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+      <c r="G12" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="e" vm="12">
         <v>#VALUE!</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
         <v>30000</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="7">
         <v>15000</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>2000</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>3</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="e" vm="13">
         <v>#VALUE!</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <v>80000</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="7">
         <v>40000</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>3000</v>
       </c>
-      <c r="F14" s="7">
-        <v>1</v>
-      </c>
-      <c r="G14" s="7">
+      <c r="F14" s="6">
+        <v>1</v>
+      </c>
+      <c r="G14" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="7">
         <v>80000</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="7">
         <v>40000</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="7">
         <v>3000</v>
       </c>
-      <c r="F15" s="7">
-        <v>1</v>
-      </c>
-      <c r="G15" s="7">
+      <c r="F15" s="6">
+        <v>1</v>
+      </c>
+      <c r="G15" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="7">
         <v>50000</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="7">
         <v>25000</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="7">
         <v>2000</v>
       </c>
-      <c r="F16" s="7">
-        <v>1</v>
-      </c>
-      <c r="G16" s="7">
+      <c r="F16" s="6">
+        <v>1</v>
+      </c>
+      <c r="G16" s="6">
         <v>2</v>
       </c>
     </row>
@@ -1760,19 +1771,19 @@
       <c r="B17" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="7">
         <v>100000</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="7">
         <v>50000</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="7">
         <v>5000</v>
       </c>
-      <c r="F17" s="7">
-        <v>1</v>
-      </c>
-      <c r="G17" s="7">
+      <c r="F17" s="6">
+        <v>1</v>
+      </c>
+      <c r="G17" s="6">
         <v>4</v>
       </c>
     </row>
@@ -1783,19 +1794,19 @@
       <c r="B18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="7">
         <v>80000</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="7">
         <v>40000</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="7">
         <v>2500</v>
       </c>
-      <c r="F18" s="7">
-        <v>1</v>
-      </c>
-      <c r="G18" s="7">
+      <c r="F18" s="6">
+        <v>1</v>
+      </c>
+      <c r="G18" s="6">
         <v>4</v>
       </c>
     </row>
@@ -1806,19 +1817,19 @@
       <c r="B19" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="7">
         <v>30000</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="7">
         <v>15000</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="7">
         <v>1700</v>
       </c>
-      <c r="F19" s="7">
-        <v>1</v>
-      </c>
-      <c r="G19" s="7">
+      <c r="F19" s="6">
+        <v>1</v>
+      </c>
+      <c r="G19" s="6">
         <v>3</v>
       </c>
     </row>
@@ -1829,24 +1840,24 @@
       <c r="B20" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="7">
         <v>80000</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="7">
         <v>40000</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="7">
         <v>2500</v>
       </c>
-      <c r="F20" s="7">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7">
+      <c r="F20" s="6">
+        <v>1</v>
+      </c>
+      <c r="G20" s="6">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="52" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="48" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>